--- a/GameConfig/Datas/运营/角色初始配置表.xlsx
+++ b/GameConfig/Datas/运营/角色初始配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\运营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AC197F-07FD-4C5A-9246-841C40D42653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B1A587-E3EF-4E25-BB7F-ABE209FE2B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>long</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -119,31 +116,7 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>初始每日购买体力次数</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>TotalRmb</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastAddStamTime</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>DailyBuyStamCount</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>初始签名</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始累计充值金额</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始上次加体力时间</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -1174,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.1640625" style="5" customWidth="1"/>
@@ -1187,13 +1160,10 @@
     <col min="9" max="10" width="28.83203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="24.9140625" style="5" customWidth="1"/>
     <col min="12" max="12" width="34.6640625" style="5" customWidth="1"/>
-    <col min="13" max="13" width="26.33203125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="29.83203125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="34.9140625" style="5" customWidth="1"/>
-    <col min="16" max="16384" width="8.6640625" style="5"/>
+    <col min="13" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,28 +1171,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>2</v>
@@ -1230,18 +1200,8 @@
       <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1249,10 +1209,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>5</v>
@@ -1264,34 +1224,24 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1304,60 +1254,46 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1386,15 +1322,6 @@
         <v>60</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5">
         <v>0</v>
       </c>
     </row>
